--- a/data/trans_camb/IP16A01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-40,4; -16,7</t>
+          <t>-37,74; -15,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-51,7; -24,57</t>
+          <t>-53,07; -24,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-58,83; -20,14</t>
+          <t>-57,06; -21,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -17,8</t>
+          <t>-43,58; -19,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,04; -16,33</t>
+          <t>-45,83; -16,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,48; -16,86</t>
+          <t>-46,49; -15,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,22; -20,26</t>
+          <t>-37,53; -20,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -23,84</t>
+          <t>-45,2; -24,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-45,27; -22,13</t>
+          <t>-45,37; -21,79</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,4; -16,7</t>
+          <t>-37,74; -15,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,7; -24,57</t>
+          <t>-53,07; -24,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,83; -20,14</t>
+          <t>-57,06; -21,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -17,8</t>
+          <t>-43,58; -19,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,04; -16,33</t>
+          <t>-45,83; -16,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,48; -16,86</t>
+          <t>-46,49; -15,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,22; -20,26</t>
+          <t>-37,53; -20,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -23,84</t>
+          <t>-45,2; -24,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,27; -22,13</t>
+          <t>-45,37; -21,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-42,31; -21,31</t>
+          <t>-41,44; -20,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-44,48; -21,57</t>
+          <t>-45,63; -22,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-66,57; -40,4</t>
+          <t>-66,94; -42,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,01; -18,69</t>
+          <t>-36,28; -18,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,99; -25,89</t>
+          <t>-48,84; -25,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,46; -26,76</t>
+          <t>-50,18; -25,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,53; -22,34</t>
+          <t>-35,96; -21,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,73; -27,1</t>
+          <t>-44,37; -26,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-54,19; -36,54</t>
+          <t>-53,69; -35,44</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,31; -21,31</t>
+          <t>-41,44; -20,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,48; -21,57</t>
+          <t>-45,63; -22,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,57; -40,4</t>
+          <t>-66,94; -42,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,01; -18,69</t>
+          <t>-36,28; -18,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,99; -25,89</t>
+          <t>-48,84; -25,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,46; -26,76</t>
+          <t>-50,18; -25,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,53; -22,34</t>
+          <t>-35,96; -21,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,73; -27,1</t>
+          <t>-44,37; -26,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,19; -36,54</t>
+          <t>-53,69; -35,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-64,72; -33,25</t>
+          <t>-64,99; -33,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-49,11; -22,05</t>
+          <t>-48,82; -22,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -33,88</t>
+          <t>-61,72; -34,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-67,41; -35,95</t>
+          <t>-67,85; -34,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-73,71; -46,04</t>
+          <t>-74,9; -47,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,11; -29,55</t>
+          <t>-54,7; -28,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,0; -37,49</t>
+          <t>-60,67; -39,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,78; -37,44</t>
+          <t>-57,35; -38,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-54,31; -34,96</t>
+          <t>-53,71; -33,89</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,72; -33,25</t>
+          <t>-64,99; -33,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-49,11; -22,05</t>
+          <t>-48,82; -22,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -33,88</t>
+          <t>-61,72; -34,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,41; -35,95</t>
+          <t>-67,85; -34,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,71; -46,04</t>
+          <t>-74,9; -47,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,11; -29,55</t>
+          <t>-54,7; -28,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,0; -37,49</t>
+          <t>-60,67; -39,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,78; -37,44</t>
+          <t>-57,35; -38,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,31; -34,96</t>
+          <t>-53,71; -33,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -16,82</t>
+          <t>-45,11; -16,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-74,94; -39,07</t>
+          <t>-73,77; -39,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-55,19; -11,19</t>
+          <t>-55,29; -11,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-76,19; -44,52</t>
+          <t>-76,23; -46,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-69,77; -33,66</t>
+          <t>-68,46; -35,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -35,34</t>
+          <t>-60,72; -35,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-56,26; -32,39</t>
+          <t>-56,02; -33,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-68,14; -41,63</t>
+          <t>-67,15; -42,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-52,68; -21,38</t>
+          <t>-52,86; -21,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -16,82</t>
+          <t>-45,11; -16,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,94; -39,07</t>
+          <t>-73,77; -39,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,19; -11,19</t>
+          <t>-55,29; -11,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,19; -44,52</t>
+          <t>-76,23; -46,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,77; -33,66</t>
+          <t>-68,46; -35,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -35,34</t>
+          <t>-60,72; -35,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,26; -32,39</t>
+          <t>-56,02; -33,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-68,14; -41,63</t>
+          <t>-67,15; -42,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,68; -21,38</t>
+          <t>-52,86; -21,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -26,63</t>
+          <t>-39,58; -27,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -32,0</t>
+          <t>-45,72; -31,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -23,97</t>
+          <t>-52,04; -25,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -31,68</t>
+          <t>-43,61; -31,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -37,17</t>
+          <t>-52,05; -37,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -33,48</t>
+          <t>-48,01; -34,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -30,87</t>
+          <t>-39,75; -30,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -36,87</t>
+          <t>-46,5; -36,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -31,58</t>
+          <t>-47,48; -32,13</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -26,63</t>
+          <t>-39,58; -27,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -32,0</t>
+          <t>-45,72; -31,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -23,97</t>
+          <t>-52,04; -25,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -31,68</t>
+          <t>-43,61; -31,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -37,17</t>
+          <t>-52,05; -37,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -33,48</t>
+          <t>-48,01; -34,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -30,87</t>
+          <t>-39,75; -30,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -36,87</t>
+          <t>-46,5; -36,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -31,58</t>
+          <t>-47,48; -32,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-37,74; -15,68</t>
+          <t>-39,28; -16,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-53,07; -24,49</t>
+          <t>-52,37; -24,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-57,06; -21,14</t>
+          <t>-55,85; -18,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-43,58; -19,55</t>
+          <t>-46,42; -19,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,83; -16,53</t>
+          <t>-45,96; -17,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,49; -15,77</t>
+          <t>-47,2; -16,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,53; -20,93</t>
+          <t>-37,59; -20,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,2; -24,3</t>
+          <t>-44,95; -23,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-45,37; -21,79</t>
+          <t>-45,96; -21,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,74; -15,68</t>
+          <t>-39,28; -16,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,07; -24,49</t>
+          <t>-52,37; -24,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,06; -21,14</t>
+          <t>-55,85; -18,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,58; -19,55</t>
+          <t>-46,42; -19,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,83; -16,53</t>
+          <t>-45,96; -17,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,49; -15,77</t>
+          <t>-47,2; -16,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,53; -20,93</t>
+          <t>-37,59; -20,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,2; -24,3</t>
+          <t>-44,95; -23,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,37; -21,79</t>
+          <t>-45,96; -21,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,44; -20,73</t>
+          <t>-41,34; -21,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-45,63; -22,96</t>
+          <t>-44,55; -21,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-66,94; -42,25</t>
+          <t>-66,7; -41,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-36,28; -18,4</t>
+          <t>-35,64; -18,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,84; -25,06</t>
+          <t>-50,38; -25,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,18; -25,45</t>
+          <t>-48,59; -25,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,96; -21,92</t>
+          <t>-36,0; -22,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,37; -26,71</t>
+          <t>-43,74; -26,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-53,69; -35,44</t>
+          <t>-55,32; -37,02</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,44; -20,73</t>
+          <t>-41,34; -21,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,63; -22,96</t>
+          <t>-44,55; -21,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,94; -42,25</t>
+          <t>-66,7; -41,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,28; -18,4</t>
+          <t>-35,64; -18,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,84; -25,06</t>
+          <t>-50,38; -25,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,18; -25,45</t>
+          <t>-48,59; -25,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,96; -21,92</t>
+          <t>-36,0; -22,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,37; -26,71</t>
+          <t>-43,74; -26,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,69; -35,44</t>
+          <t>-55,32; -37,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-64,99; -33,76</t>
+          <t>-64,63; -35,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-48,82; -22,84</t>
+          <t>-48,85; -22,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-61,72; -34,16</t>
+          <t>-60,6; -33,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-67,85; -34,0</t>
+          <t>-66,23; -34,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,9; -47,4</t>
+          <t>-75,03; -46,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,7; -28,11</t>
+          <t>-55,82; -28,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -39,61</t>
+          <t>-60,1; -38,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,35; -38,15</t>
+          <t>-57,78; -37,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-53,71; -33,89</t>
+          <t>-55,2; -35,49</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,99; -33,76</t>
+          <t>-64,63; -35,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,82; -22,84</t>
+          <t>-48,85; -22,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,72; -34,16</t>
+          <t>-60,6; -33,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,85; -34,0</t>
+          <t>-66,23; -34,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,9; -47,4</t>
+          <t>-75,03; -46,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,7; -28,11</t>
+          <t>-55,82; -28,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -39,61</t>
+          <t>-60,1; -38,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,35; -38,15</t>
+          <t>-57,78; -37,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,71; -33,89</t>
+          <t>-55,2; -35,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-45,11; -16,91</t>
+          <t>-44,7; -16,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-73,77; -39,27</t>
+          <t>-74,4; -39,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -11,28</t>
+          <t>-55,64; -10,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-76,23; -46,22</t>
+          <t>-76,09; -42,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,46; -35,15</t>
+          <t>-68,62; -32,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-60,72; -35,53</t>
+          <t>-60,45; -34,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-56,02; -33,2</t>
+          <t>-56,86; -33,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-67,15; -42,3</t>
+          <t>-67,21; -42,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-52,86; -21,64</t>
+          <t>-52,08; -20,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,11; -16,91</t>
+          <t>-44,7; -16,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,77; -39,27</t>
+          <t>-74,4; -39,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -11,28</t>
+          <t>-55,64; -10,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,23; -46,22</t>
+          <t>-76,09; -42,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,46; -35,15</t>
+          <t>-68,62; -32,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,72; -35,53</t>
+          <t>-60,45; -34,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,02; -33,2</t>
+          <t>-56,86; -33,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,15; -42,3</t>
+          <t>-67,21; -42,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,86; -21,64</t>
+          <t>-52,08; -20,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -27,1</t>
+          <t>-38,83; -26,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -31,55</t>
+          <t>-46,26; -31,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,12</t>
+          <t>-51,72; -25,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -31,13</t>
+          <t>-43,93; -30,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -37,33</t>
+          <t>-52,22; -37,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,16</t>
+          <t>-47,82; -34,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -30,8</t>
+          <t>-40,34; -30,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,5; -36,81</t>
+          <t>-47,15; -37,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -32,13</t>
+          <t>-46,8; -32,27</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -27,1</t>
+          <t>-38,83; -26,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -31,55</t>
+          <t>-46,26; -31,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,12</t>
+          <t>-51,72; -25,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -31,13</t>
+          <t>-43,93; -30,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -37,33</t>
+          <t>-52,22; -37,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,16</t>
+          <t>-47,82; -34,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -30,8</t>
+          <t>-40,34; -30,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,5; -36,81</t>
+          <t>-47,15; -37,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -32,13</t>
+          <t>-46,8; -32,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-30,64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-30,11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-28,47</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-26,26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-37,44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-36,08</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-30,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-30,11</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-30,3</t>
+          <t>-37,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-32,71</t>
+          <t>-32,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -16,36</t>
+          <t>-42,47; -17,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-52,37; -24,33</t>
+          <t>-48,04; -16,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-55,85; -18,64</t>
+          <t>-43,73; -16,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-46,42; -19,68</t>
+          <t>-40,4; -16,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,96; -17,7</t>
+          <t>-51,7; -24,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,2; -16,89</t>
+          <t>-59,66; -20,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,59; -20,28</t>
+          <t>-37,22; -20,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,95; -23,14</t>
+          <t>-44,15; -23,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-45,96; -21,86</t>
+          <t>-45,31; -21,97</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-30,64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-30,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-28,47%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-26,26%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-37,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-36,08%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-30,64%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-30,11%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-30,3%</t>
+          <t>-37,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-32,71%</t>
+          <t>-32,36%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -16,36</t>
+          <t>-42,47; -17,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,37; -24,33</t>
+          <t>-48,04; -16,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,85; -18,64</t>
+          <t>-43,73; -16,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,42; -19,68</t>
+          <t>-40,4; -16,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,96; -17,7</t>
+          <t>-51,7; -24,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,2; -16,89</t>
+          <t>-59,66; -20,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,59; -20,28</t>
+          <t>-37,22; -20,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,95; -23,14</t>
+          <t>-44,15; -23,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,96; -21,86</t>
+          <t>-45,31; -21,97</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-27,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-36,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-33,92</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-30,45</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-32,86</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-53,72</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-27,28</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-36,79</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-36,8</t>
+          <t>-50,97</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-45,05</t>
+          <t>-42,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,34; -21,14</t>
+          <t>-37,01; -18,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-44,55; -21,7</t>
+          <t>-48,99; -25,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-66,7; -41,18</t>
+          <t>-45,66; -24,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,64; -18,48</t>
+          <t>-42,31; -21,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,38; -25,77</t>
+          <t>-44,48; -21,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,59; -25,42</t>
+          <t>-62,74; -38,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,0; -22,4</t>
+          <t>-35,53; -22,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,74; -26,52</t>
+          <t>-43,73; -27,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-55,32; -37,02</t>
+          <t>-51,36; -34,64</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-27,28%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-36,79%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-33,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-30,45%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-32,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-53,72%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-27,28%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-36,79%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-36,8%</t>
+          <t>-50,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-45,05%</t>
+          <t>-42,41%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,34; -21,14</t>
+          <t>-37,01; -18,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,55; -21,7</t>
+          <t>-48,99; -25,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,7; -41,18</t>
+          <t>-45,66; -24,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,64; -18,48</t>
+          <t>-42,31; -21,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,38; -25,77</t>
+          <t>-44,48; -21,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,59; -25,42</t>
+          <t>-62,74; -38,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,0; -22,4</t>
+          <t>-35,53; -22,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,74; -26,52</t>
+          <t>-43,73; -27,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,32; -37,02</t>
+          <t>-51,36; -34,64</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-50,76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-61,25</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-40,74</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-48,77</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-34,65</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-47,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-50,76</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-61,25</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-41,55</t>
+          <t>-47,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-44,1</t>
+          <t>-43,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-64,63; -35,17</t>
+          <t>-67,41; -35,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-48,85; -22,45</t>
+          <t>-73,71; -46,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-60,6; -33,73</t>
+          <t>-54,21; -28,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-66,23; -34,95</t>
+          <t>-64,72; -33,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-75,03; -46,41</t>
+          <t>-49,11; -22,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,82; -28,22</t>
+          <t>-61,14; -34,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,1; -38,65</t>
+          <t>-60,0; -37,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,78; -37,9</t>
+          <t>-56,78; -37,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-55,2; -35,49</t>
+          <t>-54,15; -34,77</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-50,76%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-61,25%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-40,74%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-48,77%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-34,65%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-47,28%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-50,76%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-61,25%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,55%</t>
+          <t>-47,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-44,1%</t>
+          <t>-43,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,63; -35,17</t>
+          <t>-67,41; -35,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,85; -22,45</t>
+          <t>-73,71; -46,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,6; -33,73</t>
+          <t>-54,21; -28,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,23; -34,95</t>
+          <t>-64,72; -33,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,03; -46,41</t>
+          <t>-49,11; -22,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,82; -28,22</t>
+          <t>-61,14; -34,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,1; -38,65</t>
+          <t>-60,0; -37,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,78; -37,9</t>
+          <t>-56,78; -37,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,2; -35,49</t>
+          <t>-54,15; -34,77</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-61,56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-51,57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-48,03</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-29,11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-57,7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-32,47</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-61,56</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-51,57</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-47,39</t>
+          <t>-41,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-39,24</t>
+          <t>-45,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-44,7; -16,69</t>
+          <t>-76,19; -44,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-74,4; -39,55</t>
+          <t>-69,77; -33,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-55,64; -10,33</t>
+          <t>-61,24; -35,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-76,09; -42,64</t>
+          <t>-45,74; -16,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,62; -32,74</t>
+          <t>-74,94; -39,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-60,45; -34,2</t>
+          <t>-55,17; -30,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-56,86; -33,58</t>
+          <t>-56,26; -32,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-67,21; -42,1</t>
+          <t>-68,14; -41,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-52,08; -20,71</t>
+          <t>-54,53; -35,64</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-61,56%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-51,57%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-48,03%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-29,11%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-57,7%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-32,47%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-61,56%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-51,57%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-47,39%</t>
+          <t>-41,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-39,24%</t>
+          <t>-45,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,7; -16,69</t>
+          <t>-76,19; -44,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,4; -39,55</t>
+          <t>-69,77; -33,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,64; -10,33</t>
+          <t>-61,24; -35,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,09; -42,64</t>
+          <t>-45,74; -16,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,62; -32,74</t>
+          <t>-74,94; -39,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,45; -34,2</t>
+          <t>-55,17; -30,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,86; -33,58</t>
+          <t>-56,26; -32,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,21; -42,1</t>
+          <t>-68,14; -41,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,08; -20,71</t>
+          <t>-54,53; -35,64</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-37,6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-44,86</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-40,49</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-32,77</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-38,64</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-41,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-37,6</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-44,86</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-40,97</t>
+          <t>-45,47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-41,21</t>
+          <t>-42,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -26,1</t>
+          <t>-44,12; -31,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -31,83</t>
+          <t>-52,45; -37,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -25,75</t>
+          <t>-46,67; -33,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -30,9</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -37,65</t>
+          <t>-46,55; -32,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -34,11</t>
+          <t>-52,8; -38,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -30,98</t>
+          <t>-39,59; -30,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -37,11</t>
+          <t>-46,92; -36,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -32,27</t>
+          <t>-47,6; -38,07</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-37,6%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-44,86%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-40,49%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-32,77%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-38,64%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-41,47%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-37,6%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-44,86%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-40,97%</t>
+          <t>-45,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-41,21%</t>
+          <t>-42,8%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -26,1</t>
+          <t>-44,12; -31,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -31,83</t>
+          <t>-52,45; -37,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -25,75</t>
+          <t>-46,67; -33,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -30,9</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -37,65</t>
+          <t>-46,55; -32,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -34,11</t>
+          <t>-52,8; -38,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -30,98</t>
+          <t>-39,59; -30,87</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -37,11</t>
+          <t>-46,92; -36,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -32,27</t>
+          <t>-47,6; -38,07</t>
         </is>
       </c>
     </row>
